--- a/order_forms/036_final_step_confirmation--order_forms.xlsx
+++ b/order_forms/036_final_step_confirmation--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,8 +761,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,12 +790,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'credit_card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'credit_card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'bank_transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'net_30',_'label':_'net_30'}</t>
+          <t>net_30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'net_30', 'label': 'Net 30'}</t>
+          <t>Net 30</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'proforma',_'label':_'proforma'}</t>
+          <t>proforma</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'proforma', 'label': 'Proforma'}</t>
+          <t>Proforma</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'credit_card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'credit_card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'bank_transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'paid',_'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'paid', 'label': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'pending_payment',_'label':_'pending_payment'}</t>
+          <t>pending_payment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'pending_payment', 'label': 'Pending Payment'}</t>
+          <t>Pending Payment</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled',_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'cancelled', 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled',_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'cancelled', 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'approved', 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'declined',_'label':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'declined', 'label': 'Declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'pending_approval',_'label':_'pending_approval'}</t>
+          <t>pending_approval</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'pending_approval', 'label': 'Pending Approval'}</t>
+          <t>Pending Approval</t>
         </is>
       </c>
     </row>
